--- a/01_경혈별_해부생리_분석보고서/GV_독맥/GV20_백회/GV20_백회_해부생리_분석데이터.xlsx
+++ b/01_경혈별_해부생리_분석보고서/GV_독맥/GV20_백회/GV20_백회_해부생리_분석데이터.xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LayerA_papers" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_해부실체" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1234,13 +1235,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
+      <c r="B13" s="44" t="n"/>
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="44" t="n"/>
+      <c r="E13" s="44" t="n"/>
+      <c r="F13" s="44" t="n"/>
+      <c r="G13" s="44" t="n"/>
+      <c r="H13" s="45" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1523,7 +1524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.8" customWidth="1" min="1" max="1"/>
@@ -1715,6 +1716,101 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:43:54</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pubmed</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>200</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>("GV20" OR "Baihui" OR "百会") AND (acupuncture OR electroacupuncture) AND (nerve OR reflex OR autonomic OR mechanism OR anatomy) | ("GV20" OR "Baihui" OR "百会") AND ("Zhongguo Zhen Jiu"[Journal] OR "Zhen Ci Yan Jiu"[Journal])</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:43:54</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>200</v>
+      </c>
+      <c r="D7" t="n">
+        <v>24</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>doi_starts_with:10.13703,title_and_abstract.search:"Baihui" OR "GV20" | doi_starts_with:10.13702,title_and_abstract.search:"Baihui" OR "GV20" | has_doi:true,title_and_abstract.search:"Baihui" OR "GV20" AND (acupuncture OR electroacupuncture)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:43:54</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>crossref</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>200</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Baihui acupuncture nerve reflex</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:43:54</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>42</v>
+      </c>
+      <c r="E9" t="n">
+        <v>32</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>merged_into_existing=29 batch_dups=3 sources={'pubmed': 'ok', 'openalex': 'ok', 'crossref': 'ok'}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1726,7 +1822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2568,6 +2664,632 @@
       <c r="D38" t="inlineStr">
         <is>
           <t>_구판_v2.6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>FMA_해부실체 시트 신설 (2026-10-23)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>FMA 5.1.0 실체 ID·지배신경·줄기·분절·교재 비교 추가, 횡단면 모식도·FMA 경로도 추가. ARI·B-Check 불변</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>fma_query.py profile GV20; 보고서 4·6·8절·부록 A</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>교재 용어</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FMA_ID</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FMA_label</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>대응 수준</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>출처 교재</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>지배신경(FMA nerve_supply)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>상위 줄기(FMA)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>척수 분절(FMA segmental_supply)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>머리덮개널힘줄 (epicranial aponeurosis); 머리덮개널힘줄 (galea aponeurotica)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>46768</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Aponeurosis of epicranius</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>머리뼈바깥막 (pericranium)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>76623</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Pericranium</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>귓바퀴관자신경 (auriculotemporal nerve)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>53000</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Auriculotemporal nerve</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>FMA:52996 Mandibular nerve → FMA:50866 Trigeminal nerve</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>큰뒤통수신경 (great occipital nerve); 큰뒤통수신경 (greater occipital nerve)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>65443</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Greater occipital nerve</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>FMA:8788 Posterior ramus of second cervical nerve → FMA:5859 Cervical nerve</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>분절 C2(신경 줄기 추론)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>눈확위신경 (supraorbital nerve; CN5); 위눈확신경 (supraorbital nerve)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>52655</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Supra-orbital nerve</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>FMA:52638 Frontal nerve → FMA:52621 Ophthalmic nerve → FMA:50866 Trigeminal nerve</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>도르래위신경 (supratrochlear n.; CN5); 위도르래신경 (supratrochlear nerve)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>52642</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Supratrochlear nerve</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>FMA:52638 Frontal nerve → FMA:52621 Ophthalmic nerve → FMA:50866 Trigeminal nerve</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>뒤통수동ㆍ정맥 (occipital artery and vein)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>49586</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Occipital artery</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>FMA:10635 External carotid artery → FMA:3939 Common carotid artery</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>뒤통수동ㆍ정맥 (occipital artery and vein)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50802</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Occipital vein</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>FMA:4746 Deep cervical vein → FMA:4723 Brachiocephalic vein</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>FMA is_a Superior superficial cerebral vein — 분류 오류, 인용 안 함</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>얕은관자동ㆍ정맥의 마루가지 (parietal branch of the superficial temporal artery and vein)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>49670</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Parietal branch of superficial temporal artery</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>FMA:49650 Superficial temporal artery → FMA:10635 External carotid artery → FMA:3939 Common carotid artery</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>마루이끌정맥 (parietal emissary vein)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50791</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Parietal emissary vein</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>FMA:50767 Superior sagittal sinus → FMA:50764 Right transverse sinus → FMA:51293 Right sigmoid sinus → FMA:4754 Right internal jugular vein → FMA:4751 Right brachiocephalic vein → FMA:82672 Superior systemic venous tree</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>상시상정맥동 사슬 — 해부적 연결(B1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>얕은관자동ㆍ정맥 (superficial temporal artery and vein)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>49650</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Superficial temporal artery</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>FMA:10635 External carotid artery → FMA:3939 Common carotid artery</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>얕은관자동ㆍ정맥 (superficial temporal artery and vein); 얕은관자동ㆍ정맥의 마루가지 (parietal branch of the superficial temporal artery and vein)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50932</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Superficial temporal vein</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>exact/parent(branch_of)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>FMA:50928 Retromandibular vein → FMA:13110 External jugular vein → FMA:4725 Subclavian vein → FMA:4723 Brachiocephalic vein</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>김재효 마루가지는 parent(branch_of) 대응</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>분절 합집합</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>교재 비교</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>공통 6 · 공통교재 단독 2 · 김재효 단독 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FMA 5.1.0 로컬 색인, fma_query.py profile GV20 (2026-10-23). B1 보조(등록부 미등재)</t>
         </is>
       </c>
     </row>
@@ -2995,12 +3717,12 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+      <c r="E14" s="44" t="n"/>
+      <c r="F14" s="44" t="n"/>
+      <c r="G14" s="45" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -3138,12 +3860,12 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
+      <c r="B21" s="44" t="n"/>
+      <c r="C21" s="44" t="n"/>
+      <c r="D21" s="44" t="n"/>
+      <c r="E21" s="44" t="n"/>
+      <c r="F21" s="44" t="n"/>
+      <c r="G21" s="45" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
@@ -3750,11 +4472,11 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
+      <c r="B16" s="44" t="n"/>
+      <c r="C16" s="44" t="n"/>
+      <c r="D16" s="44" t="n"/>
+      <c r="E16" s="44" t="n"/>
+      <c r="F16" s="45" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3898,11 +4620,11 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="45" t="n"/>
       <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
+      <c r="D22" s="44" t="n"/>
+      <c r="E22" s="44" t="n"/>
+      <c r="F22" s="45" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="26" t="inlineStr">
@@ -4224,11 +4946,11 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
+      <c r="B11" s="44" t="n"/>
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="44" t="n"/>
+      <c r="E11" s="44" t="n"/>
+      <c r="F11" s="45" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -4798,12 +5520,12 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
+      <c r="B13" s="44" t="n"/>
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="44" t="n"/>
+      <c r="E13" s="44" t="n"/>
+      <c r="F13" s="44" t="n"/>
+      <c r="G13" s="45" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -5313,22 +6035,10 @@
           <t>통고 교차 검증</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>S_tongkao</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="D9" s="36" t="n">
-        <v>98</v>
-      </c>
-      <c r="E9" s="36" t="n">
-        <v>9.800000000000001</v>
-      </c>
+      <c r="B9" s="44" t="n"/>
+      <c r="C9" s="44" t="n"/>
+      <c r="D9" s="44" t="n"/>
+      <c r="E9" s="45" t="n"/>
       <c r="F9" s="5" t="inlineStr">
         <is>
           <t>《침구수혈통고》 5개 항목 완전 일치: ①모상건막 ②上矢狀竇 경고 ③枕大神經+眶上神經 수렴 ④旋毛中 정위 ⑤횡자 기준 ✅</t>
@@ -5363,12 +6073,12 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
+      <c r="B11" s="44" t="n"/>
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="44" t="n"/>
+      <c r="E11" s="44" t="n"/>
+      <c r="F11" s="44" t="n"/>
+      <c r="G11" s="45" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -5510,12 +6220,12 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
+      <c r="B18" s="44" t="n"/>
+      <c r="C18" s="44" t="n"/>
+      <c r="D18" s="44" t="n"/>
+      <c r="E18" s="44" t="n"/>
+      <c r="F18" s="44" t="n"/>
+      <c r="G18" s="45" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">

--- a/01_경혈별_해부생리_분석보고서/GV_독맥/GV20_백회/GV20_백회_해부생리_분석데이터.xlsx
+++ b/01_경혈별_해부생리_분석보고서/GV_독맥/GV20_백회/GV20_백회_해부생리_분석데이터.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_해부실체" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_분기추론_TriTarget" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -779,7 +780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1506,6 +1507,283 @@
       <c r="H20" s="8" t="inlineStr">
         <is>
           <t>관념 이론 노이즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-25 추가 — 《中国针灸经络通鉴》 교감 (4대 원전, Framework 2.7.7). 이 블록은 v2.7.7 정본(.md 1절)과 같은 내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>문헌</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>원문 발췌</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>한국어 요지</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>내부 포인터(파일·행)</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》 要穴</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>"百会，一名三阳五会，在前顶后一寸五分，顶中央旋毛中陷可容指，督脉、足太阳之会。刺入三分，灸三壮。"</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>위치·이명·교회·심도 일치</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_11_第贰编_第三篇_脉度、骨度与要穴.md L878</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》 足太阳</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>《灵枢·经脉》 "上额，交巅" / 《铜人》 注 "巅，顶也。顶中央有旋毛可容豆，乃三阳五会也"</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>足太阳 交巅; 可容指/可容豆 이문</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_24_第叁编_第七篇_足太阳经脉、经别、络脉和经筋.md L86·122·178·228</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Target 2 촉진 표현</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》 足厥阴</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>《灵枢·经脉》 "与督脉会于巅" / 注 "与督脉相会于巅顶之百会也"</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>족궐음 교회는 주석 단계 특정</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_29_第叁编_第十二篇_足厥阴经脉、经别、络脉和经筋.md L65·113·152</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Rank 4 후대 교회 확장</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》 督脉</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>《素问·骨空论》 "上额交巅上，入络脑" / 【按】 순행 5설 / 【按】 "《脉经》…治取顶上（百会穴），《明堂》主治同"</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>癫·痫 주치 = 顶上</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_30_第肆编_第一篇_督脉及其络脉.md L218·415·689</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》 四海</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>《灵枢·海论》 "脑为髓之海，其输上在于其盖" / 注 "其盖，即督脉经之百会"</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>원문은 其盖, 백회는 주가 특정</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_12_第贰编_第四篇_经络的标本、气街与四海.md L260·266·270</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》 《肘后》 尸厥</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>"针百会，当鼻中入发际五寸许，针入三分，补之" / 【按】 "以十二经脉、十五络脉循行皆不可解"</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>별계 정위 출처; 경락 순행 설명 불가 비판</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_07_第壹编_第五篇_不同来源的经络学说.md L300~306</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Rank 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》 脉名索引</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>◇督脉·◇督脉之别·◇督脉之络 (쪽 번호 색인)</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>색인만 — 혈위 직접 정보 없음</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_37_第伍编_附篇一_脉名索引.md L65~69</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>검색 범위 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》 전수 검색</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>天山·通百脉·泥丸·鬼门·天满·横刺(针灸大成) 검색</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>해당 0건</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴 39편 전체</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>2·3·9.1절 "4대 원전 미확인"의 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>《中国针灸证治通鉴》 한글번역</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>《圣惠》 脱肛 / 《针经摘英集》 脱肛 / 风头痛 / 《针灸捷径》 尸厥</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>1절 한국어 기술 기준(원문은 기준 텍스트)</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>中国针灸证治通鉴_21_第叁编_内科病症_四十三癞疝阴痛至四十八杂病_한글번역.md L1320·1348; 中国针灸证治通鉴_16_第叁编_内科病症_十六痹证至二十一项背痛_한글번역.md L931; 中国针灸证治通鉴_15_第叁编_内科病症_九厥证至十五疠风_한글번역.md L188</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>원문·번역 차이 없음</t>
         </is>
       </c>
     </row>
@@ -1822,7 +2100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2686,6 +2964,94 @@
       <c r="D39" t="inlineStr">
         <is>
           <t>fma_query.py profile GV20; 보고서 4·6·8절·부록 A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-25 2.7.7 · 1절</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>3대 원전</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4대 원전, 《经络通鉴》 6행(+색인·전수검색 기록) — 시트 1_문헌스크리닝DB 하단 블록</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>정본 1절·Rank 1 &amp; 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-25 2.7.7 · 1절 证治</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>자체 요약</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한글번역 문장으로 기술(21편 L1320·1348, 16편 L931, 15편 L188). 차이 없음</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>정본 Rank 1 &amp; 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-25 2.7.7 · 4.1·7절</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>고전 vs WHO, Δ 미실측, 15mm 기준</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Tri-Target: T1–T3 0mm 병합, Target 2 설정 불가(Δ 미추정), 단일 Target 1≡3, 10mm 기준; 시트 7_분기추론_TriTarget 신설</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>정본 Rank 5 Tri-Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-25 2.7.7 · 10절</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>④ 通考 교정, Δ &gt; 15mm</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>④ 通考·经络通鉴 교감 재검 — 점수 불변(71.2 ± 2.5 B, SI 75)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>정본 Rank 7</t>
         </is>
       </c>
     </row>
@@ -3298,6 +3664,346 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="46" t="inlineStr">
+        <is>
+          <t>7. 공간 변위 분기 추론 (Tri-Target, 분기 기준 Δ &gt; 10mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="46" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>정의·근거</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>포인터</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="46" t="inlineStr">
+        <is>
+          <t>Target 1 고전 문헌 위치</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>《黄帝明堂经》 "在前顶后一寸五分"(골도 성분: 前顶 3.5촌 + 1.5촌)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0 (정중선)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>앞머리털경계 위 5촌</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>피부→골막 약 5~7mm(개략)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>通考 L2433; 中国针灸经络通鉴_11_第贰编_第三篇_脉度、骨度与要穴.md L878</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="46" t="inlineStr">
+        <is>
+          <t>Target 2 촉진 실체화 위치</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>"顶中央旋毛中，陷可容指"(《明堂》), "可容豆"(《铜人》 注·《针经摘英集》), "在头中心陷者"(《圣惠》)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>특정 불가(개인별 촉지; 골도 점과의 거리 수치 없음)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>同</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>通考 L2462; 中国针灸经络通鉴_24_第叁编_第七篇_足太阳经脉、经别、络脉和经筋.md L122; 中国针灸证治通鉴_21_第叁编_内科病症_四十三癞疝阴痛至四十八杂病_한글번역.md L1320·1348; papers.id 1961(PMID 42343518 초록: 수치 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="46" t="inlineStr">
+        <is>
+          <t>Target 3 현대 WHO 위치</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>앞머리털경계 정중 직상 5촌 / 두 귀끝 연결선 중점</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>앞머리털경계 위 5촌</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>同</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>B1-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="46" t="inlineStr">
+        <is>
+          <t>자입 기준점</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>分肉·兩筋間·緣 간극 아님, 오목의 골 구조 미특정</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>간극 불명확 → 표시 안 함</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>쌍별 편차표</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="46" t="inlineStr">
+        <is>
+          <t>쌍</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Δ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="46" t="inlineStr">
+        <is>
+          <t>Target 1 – Target 3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0mm (정의상 동일)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>두 위치 모두 앞머리털경계 위 5촌(골도 정의 동일). WHO 대체 표지(귀끝 연결선 중점)와 5촌 점의 불일치는 1961 보고(수치 미공개)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>≤ 10mm → 병합(Target 1≡3)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="46" t="inlineStr">
+        <is>
+          <t>Target 1 – Target 2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>미추정</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1961 초록: 가마 투영 거리 &gt; 이론 골도 거리; 수치 없음</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>판정 불가</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="46" t="inlineStr">
+        <is>
+          <t>Target 2 – Target 3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>미추정</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1961 초록: 정수리 오목–가마, 귀끝 중점–가마 거리 ≠ 0(전자가 작음); 수치 없음</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>판정 불가</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="46" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Target 2 설정 불가(해부 공간·Δ 미특정) → Target 1 vs Target 3 비교 → 단일 Target 1≡3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1961 원문 수치로 Target 2 Δ &gt; 10mm 확인 시 독립 분기·채점 필요(단일 채점이면 예비)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>분기 기준 15mm→10mm 하향으로 분기 가능성 증가</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="46" t="inlineStr">
+        <is>
+          <t>구판 대응</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>구 T1(고전 ≈ WHO 5촌) → Target 1≡3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>구판 10.5절 'Target 2(WHO 골도 위치)' 후보 → Target 3(병합)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>위치 불변 → 구판 이중 채점 승계</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4044,7 +4750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -4657,6 +5363,13 @@
       <c r="D24" s="44" t="n"/>
       <c r="E24" s="44" t="n"/>
       <c r="F24" s="45" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>※ 2026-10-25: 위 Step 3(구판 Δ≈0.5~1.0cm, R 1.5cm)은 폐기된 구판 값. Tri-Target 판정은 시트 7_분기추론_TriTarget 참조</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -6432,7 +7145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6478,7 +7191,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6504,7 +7217,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6530,7 +7243,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6556,7 +7269,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6582,7 +7295,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6603,7 +7316,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6624,7 +7337,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6645,12 +7358,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S_orig ④ 通考 교정</t>
+          <t>S_orig ④ 通考·经络通鉴 교감</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6663,6 +7376,7 @@
         <v>62.5</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -6683,7 +7397,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6698,7 +7412,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6713,7 +7427,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6730,7 +7444,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6747,7 +7461,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6764,7 +7478,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6779,7 +7493,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6796,7 +7510,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6813,7 +7527,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6830,7 +7544,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6847,7 +7561,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1≡3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6858,6 +7572,23 @@
       <c r="C22" t="inlineStr">
         <is>
           <t>채점자 B의 상충 기록(papers.id 1961, 旋毛 위치 ≠ 골도 위치)은 정위 쟁점이며 반사 기전 상충이 아니므로 B-Check 판정에 '가설'을 적용하지 않음. 해당 쟁점은 본문 정위·분기 절에 명시. 15점 이상 불일치 항목 없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T1≡3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Framework 2.7.7 재검(2026-10-25)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>점수 불변 — 구 T1 → Target 1≡3(위치 불변), ④ 《经络通鉴》 재검(可容指/可容豆 이문, 足厥阴 교회 주석 특정, 《肘后》 入发际五寸) 결과 A 50·B 75 단계 불변. Target 2 설정 불가(Δ 미추정) — 미채점</t>
         </is>
       </c>
     </row>

--- a/01_경혈별_해부생리_분석보고서/GV_독맥/GV20_백회/GV20_백회_해부생리_분석데이터.xlsx
+++ b/01_경혈별_해부생리_분석보고서/GV_독맥/GV20_백회/GV20_백회_해부생리_분석데이터.xlsx
@@ -20,6 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_해부실체" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_분기추론_TriTarget" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-2_정위원칙_검증" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1802,7 +1803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.8" customWidth="1" min="1" max="1"/>
@@ -2089,6 +2090,101 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-29 (dry-run)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>pubmed</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>200</v>
+      </c>
+      <c r="D10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-10-23과 같은 쿼리</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-29 (dry-run)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>200</v>
+      </c>
+      <c r="D11" t="n">
+        <v>24</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-29 (dry-run)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>crossref</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>200</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-29 (dry-run)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>42</v>
+      </c>
+      <c r="E13" t="n">
+        <v>36</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>기존 병합 33 · 배치 내 중복 3 · 신규 6 DB 미병합(미러 PC). 레코드 전체: 같은 폴더 Rank6 외부검색 수집레코드 xlsx/json</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2100,7 +2196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3052,6 +3148,50 @@
       <c r="D43" t="inlineStr">
         <is>
           <t>정본 Rank 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-29 7.2절</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>두부 자세 정위 원칙 초안('입증'·'오차 없이 고정', N-I 54%)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BodyParts3D 표준 모델 실측 검증(표 7-2), 참고 이설 처리, ARI 불변</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>7-2_정위원칙_검증 시트</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-29 외부검색로그</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-23까지</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>dry-run 42건(신규 6 DB 미병합) 추가</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Rank 6 dry-run</t>
         </is>
       </c>
     </row>
@@ -3876,8 +4016,6 @@
           <t>판정</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="46" t="inlineStr">
@@ -3900,8 +4038,6 @@
           <t>≤ 10mm → 병합(Target 1≡3)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="46" t="inlineStr">
@@ -3924,8 +4060,6 @@
           <t>판정 불가</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="46" t="inlineStr">
@@ -3948,8 +4082,6 @@
           <t>판정 불가</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="46" t="inlineStr">
@@ -3972,8 +4104,6 @@
           <t>분기 기준 15mm→10mm 하향으로 분기 가능성 증가</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="46" t="inlineStr">
@@ -3996,8 +4126,789 @@
           <t>위치 불변 → 구판 이중 채점 승계</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="46" t="inlineStr">
+        <is>
+          <t>7.2 두부 자세 정위 원칙 검증 — BodyParts3D 4.0 표준 모델(피부 FMA:7163) 정중 시상 단면, Frankfurt 수평, 민감도 162조합 (중앙값 [5%, 95%])</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="46" t="inlineStr">
+        <is>
+          <t>후보점</t>
+        </is>
+      </c>
+      <c r="B3" s="46" t="inlineStr">
+        <is>
+          <t>정의</t>
+        </is>
+      </c>
+      <c r="C3" s="46" t="inlineStr">
+        <is>
+          <t>N-I 호 % 중앙값</t>
+        </is>
+      </c>
+      <c r="D3" s="46" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="E3" s="46" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="F3" s="46" t="inlineStr">
+        <is>
+          <t>Cz 대비 mm</t>
+        </is>
+      </c>
+      <c r="G3" s="46" t="inlineStr">
+        <is>
+          <t>5촌 백회 대비 mm (중앙값)</t>
+        </is>
+      </c>
+      <c r="H3" s="46" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="I3" s="46" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="J3" s="46" t="inlineStr">
+        <is>
+          <t>최고점 만드는 굴곡(°)</t>
+        </is>
+      </c>
+      <c r="K3" s="46" t="inlineStr">
+        <is>
+          <t>아래 피질</t>
+        </is>
+      </c>
+      <c r="L3" s="46" t="inlineStr">
+        <is>
+          <t>Target 처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Vertex FMA:46484</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Frankfurt 수평 최고점</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-50.7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-88.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-103.7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-74</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>위이마이랑</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>해당 없음(자세 정의점)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>直兩耳尖</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>귀끝 Frankfurt 수직선 × 정중선</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-17.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-55.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-74.90000000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-36.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>위이마이랑</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>후대 이설(원 《十四经发挥》~) — 참고 이설</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cz</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>N-I 50%</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-38.2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-43.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-33.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>위이마이랑</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>해당 없음(두개계측점)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Taylor-Haughton 54%</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cz + 약 2cm</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>54</v>
+      </c>
+      <c r="D7" t="n">
+        <v>54</v>
+      </c>
+      <c r="E7" t="n">
+        <v>54</v>
+      </c>
+      <c r="F7" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-23.3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-28.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-18.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>중심앞이랑</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>해당 없음(두개계측점)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>귓불→귀끝 연장선</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4점 평면 × 정중선</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-20.8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-41.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>중심앞이랑</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>개인 제안 정위 — 참고 이설</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>가쪽반고리관 수평 β=20°</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CT 평균(Reid)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-45</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-13.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>위이마이랑~중심앞이랑</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>개인 제안 정위 — 참고 이설</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>가쪽반고리관 수평 β=23.4°</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CT 평균 Frankfurt 환산</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-21</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-35.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>중심앞이랑</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>개인 제안 정위 — 참고 이설</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>가쪽반고리관 수평 β=30°</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>임상 관례</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-23.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>30</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>중심앞·뒤이랑 경계</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>개인 제안 정위 — 참고 이설</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>골도 5촌 백회</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Target 1≡3 환산</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>중심뒤이랑</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Target 1≡3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>입력·가정</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>근거 포인터</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>orbitale (모델 좌표 y, z mm)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>-145.2, 1500.8</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>머리뼈 메쉬 정면 광선 깊이맵(눈확 아래 테두리 최저점, 좌우 평균)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>porion z (mm)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1505.8 (기본) / 1510.0</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>외측 깊이맵 바깥귀길 오목: 중심 1501.2, 위끝 상한 1510.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>모델의 Frankfurt 대비 굴곡</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4.6° / 8.4°</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>porion–orbitale 기울기</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>연조직 nasion (y, z)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>-181.5, 1536.4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>이마–코 사이 피부 윤곽 최심점</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>inion 높이 z</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1500 / 1510 / 1520</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>뒤통수→목 꺾임점(GV17 枕外隆凸上缘 대용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>귀끝 위치 (porion 기준 뒤, 위 mm)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>(5,25) / (15,30) / (25,35)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>피부 메쉬에 귓바퀴 없음 — 가정</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>귀 장축 기울기</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>14.6 / 19.4 / 24.2°</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PMID 37643081 (남성 19.40 ± 4.83°)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>앞머리털경계 (N 기준 호 mm)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>50 / 60 / 70</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>가정</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>골도 5촌 백회</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>trichion + 5/9.5 × (inion − trichion)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>前发际→GV20 5촌, GV20→GV17 4.5촌</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>가쪽반고리관 기울기</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>19.9 ± 7.0° (Reid) → Frankfurt 약 23.4°; 임상 관례 30°</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PMID 16088383</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>접선 평활</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>가우시안 σ = 8mm(16표본×0.5mm)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>피부 메쉬 요철 ±1mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>머리뼈 교차 확인</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>30° 굴곡 시 최고점 이동: 머리뼈 56mm, 피부 77mm</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>이마·마루·뒤통수뼈 메쉬</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>피질 대응</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SFG ≤52% · PreCG 53–57% · PostCG 57–61% · SPL ≥62%</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BodyParts3D 이랑 메쉬 최근접(두피–피질 12~18mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>원전 대조</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>直两耳尖 최초 《十四经发挥》; 略退些子 《针灸聚英》·《循经考穴编》; 两耳尖折中 《医方类聚》; 耳垂 정위 0건</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>穴位通鉴 05_督脉(2) L2124·L2136·L2170; 腧穴通考 22 督脉穴-2 L759; 证治通鉴 22 L1288 / 한글번역 L1989</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>그림</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>그림 4-2 (국문·영문 PNG)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>acupoint_anatomy scripts/fma/figures/GV20_posture_localization.py</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7376,7 +8287,6 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
